--- a/Output/validation_mot/validation_workbook.xlsx
+++ b/Output/validation_mot/validation_workbook.xlsx
@@ -12,11 +12,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4_trip_length_KS" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5_CR_vs_cellular" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7_transit_OD_fit" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_time_of_day" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_cordon_sectors" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T14_bus_origins" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T15_rail_stations" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T17_running_times" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7b_bus_pattern" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_time_of_day" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_cordon_sectors" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T14_bus_origins" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T15_rail_stations" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T17_running_times" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -524,6 +525,1342 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>T15_rail_stations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>what</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>obs_total</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mod_total</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>total_diff_pct</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>slope_origin</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>R2_origin</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>RMSE_pct</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>station-pair matrix, common stations</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>182</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1799.472</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-50.721</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.669</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28.638</v>
+      </c>
+      <c r="K4" t="n">
+        <v>142.735</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.749</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>station entries</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1799.472</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-50.721</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I5" t="n">
+        <v>132.294</v>
+      </c>
+      <c r="J5" t="n">
+        <v>186.082</v>
+      </c>
+      <c r="K5" t="n">
+        <v>71.343</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>station entries, after one scale factor (2.03)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.982</v>
+      </c>
+      <c r="I6" t="n">
+        <v>38.867</v>
+      </c>
+      <c r="J6" t="n">
+        <v>48.033</v>
+      </c>
+      <c r="K6" t="n">
+        <v>18.416</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.861</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>station exits</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1799.472</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-50.721</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="I7" t="n">
+        <v>132.294</v>
+      </c>
+      <c r="J7" t="n">
+        <v>228.123</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.461</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>station exits, after one scale factor (2.03)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3651.593</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.976</v>
+      </c>
+      <c r="I8" t="n">
+        <v>43.344</v>
+      </c>
+      <c r="J8" t="n">
+        <v>68.444</v>
+      </c>
+      <c r="K8" t="n">
+        <v>26.241</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.847</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T15_rail_station_size_classes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>what</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>class</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>obs_mean</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RMSE_pct</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>limit_pct</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" t="n">
+        <v>56.712</v>
+      </c>
+      <c r="F14" t="n">
+        <v>41.326</v>
+      </c>
+      <c r="G14" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>100-250</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>173.236</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50.135</v>
+      </c>
+      <c r="G15" t="n">
+        <v>40</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>250-500</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>493.552</v>
+      </c>
+      <c r="F16" t="n">
+        <v>56.423</v>
+      </c>
+      <c r="G16" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>500-750</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>612.062</v>
+      </c>
+      <c r="F17" t="n">
+        <v>52.168</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>750-1000</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>873.427</v>
+      </c>
+      <c r="F18" t="n">
+        <v>55.653</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>56.712</v>
+      </c>
+      <c r="F19" t="n">
+        <v>21.513</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>100-250</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>173.236</v>
+      </c>
+      <c r="F20" t="n">
+        <v>27.735</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>250-500</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>493.552</v>
+      </c>
+      <c r="F21" t="n">
+        <v>11.572</v>
+      </c>
+      <c r="G21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>500-750</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>612.062</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.936</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>entries</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>750-1000</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>873.427</v>
+      </c>
+      <c r="F23" t="n">
+        <v>10.008</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>6</v>
+      </c>
+      <c r="E24" t="n">
+        <v>41.351</v>
+      </c>
+      <c r="F24" t="n">
+        <v>53.145</v>
+      </c>
+      <c r="G24" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>100-250</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>133.792</v>
+      </c>
+      <c r="F25" t="n">
+        <v>59.478</v>
+      </c>
+      <c r="G25" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>500-750</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>676.163</v>
+      </c>
+      <c r="F26" t="n">
+        <v>35.212</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>750-1000</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>870.867</v>
+      </c>
+      <c r="F27" t="n">
+        <v>55.732</v>
+      </c>
+      <c r="G27" t="n">
+        <v>15</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>as is</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1000+</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1187.5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>53.376</v>
+      </c>
+      <c r="G28" t="n">
+        <v>12</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0-100</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="n">
+        <v>41.351</v>
+      </c>
+      <c r="F29" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>100-250</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>133.792</v>
+      </c>
+      <c r="F30" t="n">
+        <v>24.469</v>
+      </c>
+      <c r="G30" t="n">
+        <v>40</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>500-750</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>676.163</v>
+      </c>
+      <c r="F31" t="n">
+        <v>31.472</v>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>750-1000</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>870.867</v>
+      </c>
+      <c r="F32" t="n">
+        <v>10.169</v>
+      </c>
+      <c r="G32" t="n">
+        <v>15</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>exits</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>scaled</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1000+</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1187.5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5.388</v>
+      </c>
+      <c r="G33" t="n">
+        <v>12</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>T15_rail_origins_by_superzone</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>survey rail 2022 (door-to-door)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>station 2019 x 0.793</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>rail 2025 stations</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" t="n">
+        <v>566.8</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1951.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="n">
+        <v>818.8</v>
+      </c>
+      <c r="C40" t="n">
+        <v>576.1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1168.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" t="n">
+        <v>440.6</v>
+      </c>
+      <c r="C41" t="n">
+        <v>526.9</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1279.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B42" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>557.6</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>8</v>
+      </c>
+      <c r="B44" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="C44" t="n">
+        <v>167</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1303.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>11</v>
+      </c>
+      <c r="B45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>12</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>304.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>500.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>13</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>160.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>14</v>
+      </c>
+      <c r="B48" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>15</v>
+      </c>
+      <c r="B49" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="C49" t="n">
+        <v>234</v>
+      </c>
+      <c r="D49" t="n">
+        <v>599.4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>16</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>17</v>
+      </c>
+      <c r="B51" t="n">
+        <v>35</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>21</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>207.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>22</v>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>155.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>346.9</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>24</v>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>181.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>25</v>
+      </c>
+      <c r="B55" t="n">
+        <v>138.7</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>34</v>
+      </c>
+      <c r="B56" t="n">
+        <v>301.8</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>36</v>
+      </c>
+      <c r="B57" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>709.5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>37</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>314.3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>39</v>
+      </c>
+      <c r="B59" t="n">
+        <v>554.9</v>
+      </c>
+      <c r="C59" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>508.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>40</v>
+      </c>
+      <c r="B60" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="C60" t="n">
+        <v>141.6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>205.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -900,18 +2237,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="70" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
-    <col width="57" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1939,90 +3276,90 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T7b</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Haifa city inbound</t>
+          <t>destination pattern: A (RavKav alightings) vs B (RavKav production x on-board), survey bus trips as evidence</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>cordon, hourly 06-19</t>
+          <t>origin super-zone, destination 1250-zone</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CR &gt; 0.6</t>
+          <t>lower JSD / higher CR against the survey</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CR 0.78 (06-09 only: 0.72); AM share of 06-19: survey 0.34 vs counts 0.22</t>
+          <t>JSD A 0.365 vs B 0.540; CR A 0.33 vs B 0.20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>finding</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Shape agreement of the whole-day profile; the survey puts more of the day in the morning peak than the road does (see the AM shares and the next table).</t>
+          <t>Evidence for the choice of the destination pattern; the guideline sets no criterion for it.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>survey 2017/18; counts 2017-2023</t>
+          <t>survey bus trips 2017/18 (independent of A, B, E); RavKav May 2022; on-board survey</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T8</t>
+          <t>T7b</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Haifa city outbound</t>
+          <t>split inside the destination super-zone: A vs B vs E</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>cordon, hourly 06-19</t>
+          <t>destination 1250-zone given destination super-zone</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CR &gt; 0.6</t>
+          <t>lower JSD / higher CR</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CR 0.77 (06-09 only: 0.73); AM share of 06-19: survey 0.16 vs counts 0.19</t>
+          <t>JSD A 0.288, B 0.356, E 0.358</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pass</t>
+          <t>finding</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Shape agreement of the whole-day profile; the survey puts more of the day in the morning peak than the road does (see the AM shares and the next table).</t>
+          <t>Isolates the fine pattern: does the on-board survey place the trips better inside a super-zone than RavKav's inferred alighting zone?</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>survey 2017/18; counts 2017-2023</t>
+          <t>as above</t>
         </is>
       </c>
     </row>
@@ -2037,7 +3374,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Krayot inbound</t>
+          <t>departure profile vs counts, Haifa city inbound</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2052,7 +3389,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CR 0.75 (06-09 only: 0.71); AM share of 06-19: survey 0.21 vs counts 0.22</t>
+          <t>CR 0.78 (06-09 only: 0.72); AM share of 06-19: survey 0.34 vs counts 0.22</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2082,7 +3419,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Krayot outbound</t>
+          <t>departure profile vs counts, Haifa city outbound</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2097,7 +3434,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CR 0.77 (06-09 only: 0.73); AM share of 06-19: survey 0.27 vs counts 0.17</t>
+          <t>CR 0.77 (06-09 only: 0.73); AM share of 06-19: survey 0.16 vs counts 0.19</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2127,7 +3464,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Kiryat Ata + Zevulun inbound</t>
+          <t>departure profile vs counts, Krayot inbound</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2142,7 +3479,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CR 0.79 (06-09 only: 0.82); AM share of 06-19: survey 0.18 vs counts 0.20</t>
+          <t>CR 0.75 (06-09 only: 0.71); AM share of 06-19: survey 0.21 vs counts 0.22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2172,7 +3509,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Kiryat Ata + Zevulun outbound</t>
+          <t>departure profile vs counts, Krayot outbound</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2187,7 +3524,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CR 0.71 (06-09 only: 0.71); AM share of 06-19: survey 0.33 vs counts 0.20</t>
+          <t>CR 0.77 (06-09 only: 0.73); AM share of 06-19: survey 0.27 vs counts 0.17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2217,7 +3554,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Nazareth + Nof HaGalil inbound</t>
+          <t>departure profile vs counts, Kiryat Ata + Zevulun inbound</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2232,7 +3569,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CR 0.66 (06-09 only: 0.78); AM share of 06-19: survey 0.18 vs counts 0.19</t>
+          <t>CR 0.79 (06-09 only: 0.82); AM share of 06-19: survey 0.18 vs counts 0.20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2262,7 +3599,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Nazareth + Nof HaGalil outbound</t>
+          <t>departure profile vs counts, Kiryat Ata + Zevulun outbound</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2277,7 +3614,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CR 0.63 (06-09 only: 0.64); AM share of 06-19: survey 0.40 vs counts 0.28</t>
+          <t>CR 0.71 (06-09 only: 0.71); AM share of 06-19: survey 0.33 vs counts 0.20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2307,7 +3644,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Tirat Carmel inbound</t>
+          <t>departure profile vs counts, Nazareth + Nof HaGalil inbound</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2322,7 +3659,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CR 0.73 (06-09 only: 0.61); AM share of 06-19: survey 0.22 vs counts 0.23</t>
+          <t>CR 0.66 (06-09 only: 0.78); AM share of 06-19: survey 0.18 vs counts 0.19</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2352,7 +3689,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Tirat Carmel outbound</t>
+          <t>departure profile vs counts, Nazareth + Nof HaGalil outbound</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2367,7 +3704,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CR 0.77 (06-09 only: 0.77); AM share of 06-19: survey 0.30 vs counts 0.23</t>
+          <t>CR 0.63 (06-09 only: 0.64); AM share of 06-19: survey 0.40 vs counts 0.28</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2397,7 +3734,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Metropolitan core inbound</t>
+          <t>departure profile vs counts, Tirat Carmel inbound</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2412,7 +3749,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CR 0.77 (06-09 only: 0.75); AM share of 06-19: survey 0.37 vs counts 0.25</t>
+          <t>CR 0.73 (06-09 only: 0.61); AM share of 06-19: survey 0.22 vs counts 0.23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2442,7 +3779,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>departure profile vs counts, Metropolitan core outbound</t>
+          <t>departure profile vs counts, Tirat Carmel outbound</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2457,7 +3794,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CR 0.73 (06-09 only: 0.80); AM share of 06-19: survey 0.17 vs counts 0.20</t>
+          <t>CR 0.77 (06-09 only: 0.77); AM share of 06-19: survey 0.30 vs counts 0.23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2487,12 +3824,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>departure profile vs RavKav boardings, bus (public bus + Metronit)</t>
+          <t>departure profile vs counts, Metropolitan core inbound</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>quarter-hour 06-09</t>
+          <t>cordon, hourly 06-19</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2502,7 +3839,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CR 0.75; busiest hour holds 0.59 of the three hours in the survey vs 0.48 in RavKav</t>
+          <t>CR 0.77 (06-09 only: 0.75); AM share of 06-19: survey 0.37 vs counts 0.25</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2512,12 +3849,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Departure time (survey) is not boarding time (RavKav) and the years differ (2017/18 vs 2025); the survey peak is sharper.</t>
+          <t>Shape agreement of the whole-day profile; the survey puts more of the day in the morning peak than the road does (see the AM shares and the next table).</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>survey 2017/18; RavKav 2025 (42 Tuesdays)</t>
+          <t>survey 2017/18; counts 2017-2023</t>
         </is>
       </c>
     </row>
@@ -2532,12 +3869,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>departure profile vs RavKav boardings, Metronit only (mode 5)</t>
+          <t>departure profile vs counts, Metropolitan core outbound</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>quarter-hour 06-09</t>
+          <t>cordon, hourly 06-19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2547,7 +3884,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CR 0.74; busiest hour holds 0.53 of the three hours in the survey vs 0.43 in RavKav</t>
+          <t>CR 0.73 (06-09 only: 0.80); AM share of 06-19: survey 0.17 vs counts 0.20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2557,102 +3894,102 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Departure time (survey) is not boarding time (RavKav) and the years differ (2017/18 vs 2025); the survey peak is sharper.</t>
+          <t>Shape agreement of the whole-day profile; the survey puts more of the day in the morning peak than the road does (see the AM shares and the next table).</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>survey 2017/18; RavKav 2025 (42 Tuesdays)</t>
+          <t>survey 2017/18; counts 2017-2023</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cordon sectors vs counts: all testable sector cells, 06-09</t>
+          <t>departure profile vs RavKav boardings, bus (public bus + Metronit)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>44 cordon-sector-direction cells</t>
+          <t>quarter-hour 06-09</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>each cell ±15 %; RMSE% &lt; 35 %</t>
+          <t>CR &gt; 0.6</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>survey / count = 0.71 in total; 16% of cells within ±15 %; RMSE% 51; slope 0.68; R2 0.60</t>
+          <t>CR 0.75; busiest hour holds 0.59 of the three hours in the survey vs 0.48 in RavKav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>miss (explained)</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Residents-only AM layer against all traffic (trucks, vans, taxis, buses, non-residents, trips with an end outside the study area and through traffic on Roads 2, 4, 70, 79 are not in the layer); sectors with most links imputed say more about the imputation than the layer. Reported, not adjusted.</t>
+          <t>Departure time (survey) is not boarding time (RavKav) and the years differ (2017/18 vs 2025); the survey peak is sharper.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>car layer 2022 (survey 2017/18); counts 2017-2023</t>
+          <t>survey 2017/18; RavKav 2025 (42 Tuesdays)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T12</t>
+          <t>T8</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>cordon sectors vs counts: cells with &gt;= 50 % of the PCE counted, 06-09</t>
+          <t>departure profile vs RavKav boardings, Metronit only (mode 5)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>21 cordon-sector-direction cells</t>
+          <t>quarter-hour 06-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>each cell ±15 %; RMSE% &lt; 35 %</t>
+          <t>CR &gt; 0.6</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>survey / count = 0.58 in total; 0% of cells within ±15 %; RMSE% 62; slope 0.53; R2 0.31</t>
+          <t>CR 0.74; busiest hour holds 0.53 of the three hours in the survey vs 0.43 in RavKav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>miss (explained)</t>
+          <t>pass</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Residents-only AM layer against all traffic (trucks, vans, taxis, buses, non-residents, trips with an end outside the study area and through traffic on Roads 2, 4, 70, 79 are not in the layer); sectors with most links imputed say more about the imputation than the layer. Reported, not adjusted.</t>
+          <t>Departure time (survey) is not boarding time (RavKav) and the years differ (2017/18 vs 2025); the survey peak is sharper.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>car layer 2022 (survey 2017/18); counts 2017-2023</t>
+          <t>survey 2017/18; RavKav 2025 (42 Tuesdays)</t>
         </is>
       </c>
     </row>
@@ -2667,7 +4004,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>cordon sectors vs counts: all testable sector cells, 07-08 peak hour</t>
+          <t>cordon sectors vs counts: all testable sector cells, 06-09</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2682,7 +4019,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>survey / count = 1.19 in total; 20% of cells within ±15 %; RMSE% 59; slope 1.15; R2 0.61</t>
+          <t>survey / count = 0.71 in total; 16% of cells within ±15 %; RMSE% 51; slope 0.68; R2 0.60</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2712,7 +4049,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>cordon sectors vs counts: cells with &gt;= 50 % counted, 07-08 peak hour</t>
+          <t>cordon sectors vs counts: cells with &gt;= 50 % of the PCE counted, 06-09</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2727,7 +4064,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>survey / count = 1.00 in total; 24% of cells within ±15 %; RMSE% 53; slope 0.91; R2 0.30</t>
+          <t>survey / count = 0.58 in total; 0% of cells within ±15 %; RMSE% 62; slope 0.53; R2 0.31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2749,30 +4086,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>bus origin totals by super-zone vs RavKav 2022: all super-zones</t>
+          <t>cordon sectors vs counts: all testable sector cells, 07-08 peak hour</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>36 super-zones</t>
+          <t>44 cordon-sector-direction cells</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>each zone within ±15 %</t>
+          <t>each cell ±15 %; RMSE% &lt; 35 %</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>53% of zones within ±15 %; layer / RavKav = 1.28; R2 0.40, slope 1.13, RMSE% 72</t>
+          <t>survey / count = 1.19 in total; 20% of cells within ±15 %; RMSE% 59; slope 1.15; R2 0.61</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2782,57 +4119,57 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Mixture of the anchored and guarded zones: see the two rows below.</t>
+          <t>Residents-only AM layer against all traffic (trucks, vans, taxis, buses, non-residents, trips with an end outside the study area and through traffic on Roads 2, 4, 70, 79 are not in the layer); sectors with most links imputed say more about the imputation than the layer. Reported, not adjusted.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>bus 2022 layer vs RavKav May 2022 / 2025</t>
+          <t>car layer 2022 (survey 2017/18); counts 2017-2023</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>bus origin totals by super-zone vs RavKav 2022: mostly anchored super-zones</t>
+          <t>cordon sectors vs counts: cells with &gt;= 50 % counted, 07-08 peak hour</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22 super-zones</t>
+          <t>21 cordon-sector-direction cells</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>each zone within ±15 %</t>
+          <t>each cell ±15 %; RMSE% &lt; 35 %</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>82% of zones within ±15 %; layer / RavKav = 0.99; R2 0.97, slope 1.00, RMSE% 8</t>
+          <t>survey / count = 1.00 in total; 24% of cells within ±15 %; RMSE% 53; slope 0.91; R2 0.30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>miss (unexplained)</t>
+          <t>miss (explained)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Agreement is expected (anchored cells take RavKav volume by construction), so this row is not evidence for the layer. Zones outside +/-15 % (difference, share of the survey volume that is guarded): 3 (-23 %, 0%), 12 (-35 %, 0%), 13 (+20 %, 0%), 20 (+18 %, 46%). Not explained yet: candidates are the home-based re-allocation of origins to TAZs (calibration step 3) and the two super-zone keys that disagree for 142 TAZs (T1).</t>
+          <t>Residents-only AM layer against all traffic (trucks, vans, taxis, buses, non-residents, trips with an end outside the study area and through traffic on Roads 2, 4, 70, 79 are not in the layer); sectors with most links imputed say more about the imputation than the layer. Reported, not adjusted.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>bus 2022 layer vs RavKav May 2022 / 2025</t>
+          <t>car layer 2022 (survey 2017/18); counts 2017-2023</t>
         </is>
       </c>
     </row>
@@ -2847,12 +4184,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>bus origin totals by super-zone vs RavKav 2022: mostly guarded super-zones</t>
+          <t>bus origin totals by super-zone vs RavKav 2022: all super-zones</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>14 super-zones</t>
+          <t>36 super-zones</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2862,7 +4199,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7% of zones within ±15 %; layer / RavKav = 2.36; R2 0.42, slope 2.30, RMSE% 215</t>
+          <t>53% of zones within ±15 %; layer / RavKav = 1.28; R2 0.40, slope 1.13, RMSE% 72</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2872,7 +4209,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>In guarded cells the survey volume is kept because RavKav records under half of it (coverage: operators, cash fares, un-geocoded stops, with the data provider). This is the rule working as designed, and the test of it.</t>
+          <t>Mixture of the anchored and guarded zones: see the two rows below.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2884,7 +4221,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2892,22 +4229,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>rail station-pair matrix, 2019 x 0.793 vs 2025 taps</t>
+          <t>bus origin totals by super-zone vs RavKav 2022: mostly anchored super-zones</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14 common stations</t>
+          <t>22 super-zones</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>R2 &gt; 0.85 and slope 0.9-1.1</t>
+          <t>each zone within ±15 %</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>R2 0.94, slope 0.44, RMSE% 143, CR 0.75</t>
+          <t>82% of zones within ±15 %; layer / RavKav = 0.99; R2 0.97, slope 1.00, RMSE% 8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2917,19 +4254,19 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Six years apart: the 2025 taps carry 2.0 x the 2019 smart-card trips on the same stations; the pattern (R2) is the informative part. Not adjusted.</t>
+          <t>Anchored cells take RavKav's volume only in segments with at least 5 sampled survey trips; thinner segments inherit the origin-wide ratio, so the origin total is not RavKav's even when nothing is guarded. Where no volume is guarded the rule reproduces the layer to within a trip (column "volume the rule gives"; guarded cells are grown to 2022 on top). Zones outside +/-15 %: 3 (-23 %; thin segments account for -663 of the +663 trips), 12 (-35 %; thin segments account for -770 of the +770 trips), 13 (+20 %; thin segments account for +351 of the -351 trips), 20 (+18 %; thin segments account for -186 of the -508 trips).</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2019 station matrix x 0.793 vs RavKav rail 2025</t>
+          <t>bus 2022 layer vs RavKav May 2022 / 2025</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>T15</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -2937,22 +4274,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rail station entries, aggregate RMSE%</t>
+          <t>bus origin totals by super-zone vs RavKav 2022: mostly guarded super-zones</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>14 stations</t>
+          <t>14 super-zones</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RMSE% &lt; 35 %</t>
+          <t>each zone within ±15 %</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>RMSE% 71 as is; 18 after one scale factor; R2 0.96</t>
+          <t>7% of zones within ±15 %; layer / RavKav = 2.36; R2 0.42, slope 2.30, RMSE% 215</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2962,12 +4299,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>The scale gap (2019 vs 2025) dominates the as-is figure; the scaled figure shows the station pattern.</t>
+          <t>In guarded cells the survey volume is kept because RavKav records under half of it (coverage: operators, cash fares, un-geocoded stops, with the data provider). This is the rule working as designed, and the test of it.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2019 station matrix x 0.793 vs RavKav rail 2025</t>
+          <t>bus 2022 layer vs RavKav May 2022 / 2025</t>
         </is>
       </c>
     </row>
@@ -2982,12 +4319,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>survey door-to-door rail vs station origins</t>
+          <t>rail station-pair matrix, 2019 x 0.793 vs 2025 taps</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>super-zone</t>
+          <t>14 common stations</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2997,29 +4334,29 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>R2 0.52, slope 0.36</t>
+          <t>R2 0.94, slope 0.44, RMSE% 143, CR 0.75</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>not applicable (different frame)</t>
+          <t>miss (explained)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Home zone vs station: the survey has 54 rail trips and mostly crosses the study boundary; the station matrix is the rail layer to use for loading.</t>
+          <t>Six years apart: the 2025 taps carry 2.0 x the 2019 smart-card trips on the same stations; the pattern (R2) is the informative part. Not adjusted.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>rail 2022 survey layer vs rail 2025 stations</t>
+          <t>2019 station matrix x 0.793 vs RavKav rail 2025</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3027,22 +4364,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>running time, scheduled vs measured: bus, covered &gt;= 80 %</t>
+          <t>rail station entries, aggregate RMSE%</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6372 trips</t>
+          <t>14 stations</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>within ±15 % in &gt;= 85 % of trips</t>
+          <t>RMSE% &lt; 35 %</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>52% of trips within ±15 %; observed / scheduled 1.13 (aggregate), R2 0.70</t>
+          <t>RMSE% 71 as is; 18 after one scale factor; R2 0.96</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3052,19 +4389,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tests the timetable against measured link speeds (May 2026 speeds, 2 June 2026 timetable); short trips and long arterial hops run slower than scheduled (step 30).</t>
+          <t>The scale gap (2019 vs 2025) dominates the as-is figure; the scaled figure shows the station pattern.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GTFS 22 May 2026; link speeds May 2026</t>
+          <t>2019 station matrix x 0.793 vs RavKav rail 2025</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T15</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3072,37 +4409,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>running time, scheduled vs measured: Metronit (BRT), covered &gt;= 80 %</t>
+          <t>survey door-to-door rail vs station origins</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>267 trips</t>
+          <t>super-zone</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>within ±10 % in &gt;= 85 % of trips</t>
+          <t>R2 &gt; 0.85 and slope 0.9-1.1</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>8% of trips within ±10 %; observed / scheduled 0.89 (aggregate), R2 0.87</t>
+          <t>R2 0.52, slope 0.36</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>miss (explained)</t>
+          <t>not applicable (different frame)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Tests the timetable against measured link speeds (May 2026 speeds, 2 June 2026 timetable); short trips and long arterial hops run slower than scheduled (step 30).</t>
+          <t>Home zone vs station: the survey has 54 rail trips and mostly crosses the study boundary; the station matrix is the rail layer to use for loading.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GTFS 22 May 2026; link speeds May 2026</t>
+          <t>rail 2022 survey layer vs rail 2025 stations</t>
         </is>
       </c>
     </row>
@@ -3117,35 +4454,125 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>running time, scheduled vs measured: bus, covered &gt;= 80 %</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>6372 trips</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>within ±15 % in &gt;= 85 % of trips</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>52% of trips within ±15 %; observed / scheduled 1.13 (aggregate), R2 0.70</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>miss (explained)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Tests the timetable against measured link speeds (May 2026 speeds, 2 June 2026 timetable); short trips and long arterial hops run slower than scheduled (step 30).</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>GTFS 22 May 2026; link speeds May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>running time, scheduled vs measured: Metronit (BRT), covered &gt;= 80 %</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>267 trips</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>within ±10 % in &gt;= 85 % of trips</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>8% of trips within ±10 %; observed / scheduled 0.89 (aggregate), R2 0.87</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>miss (explained)</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Tests the timetable against measured link speeds (May 2026 speeds, 2 June 2026 timetable); short trips and long arterial hops run slower than scheduled (step 30).</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>GTFS 22 May 2026; link speeds May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>GTFS door-to-door vs survey-reported bus time, area pairs</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>33 pairs</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>within ±15 % in &gt;= 85 % of pairs</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>6% of pairs within ±15 %; median survey / GTFS 1.52</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>miss (explained)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>A fixed overhead of about 9 minutes door to door (access, waiting for unreliable service, transfers) is missing from the GTFS time (handover C4).</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>survey 2017/18 vs GTFS 2026</t>
         </is>
@@ -39350,6 +40777,3271 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H174"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="51" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>BusPattern_survey_destination_prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>origin super-zones used</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sampled trips behind them</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>JSD (trip-weighted, lower is better)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CR (trip-weighted, higher is better)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>destination super-zone</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1295</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6088</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>destination 1250-zone</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3276</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>split inside destination super-zone</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4202</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>destination super-zone</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>26</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3978</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>destination 1250-zone</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1986</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>split inside destination super-zone</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>26</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3404</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>destination super-zone</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>26</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>destination 1250-zone</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2646</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>split inside destination super-zone</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>26</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.3395</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>destination super-zone</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>26</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7417</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>destination 1250-zone</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>26</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3718</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>split inside destination super-zone</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>26</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.4367</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>destination super-zone</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>26</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.0212</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.8292</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>destination 1250-zone</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4584</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>split inside destination super-zone</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>26</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1695</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2075</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5204</v>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BusPattern_bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JSD A</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.4326</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.4533</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JSD B</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5945</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5702</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6165</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JSD E</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5139</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>B - A</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.1391</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A - E</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.0614</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.07779999999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.0471</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BusPattern_trip_length_and_local_share</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>median km</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mean km</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>share inside one 1250-zone</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>share inside one super-zone</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>KS D</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>critical (5 %)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>survey (reported distance)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.905</v>
+      </c>
+      <c r="C34" t="n">
+        <v>6.3906</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.5086000000000001</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>3.5124</v>
+      </c>
+      <c r="C35" t="n">
+        <v>6.9907</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.1109</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.4395</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.07820000000000001</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>6.3247</v>
+      </c>
+      <c r="C36" t="n">
+        <v>13.6348</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.0538</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.2404</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.1042</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.0793</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1379</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4.5959</v>
+      </c>
+      <c r="C38" t="n">
+        <v>8.1074</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0838</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4.7887</v>
+      </c>
+      <c r="C39" t="n">
+        <v>8.4367</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="H39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BusPattern_by_origin_superzone</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>pattern</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>origin super-zone</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>sampled trips</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>JSD</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>36</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6736</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.1224</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="n">
+        <v>46</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.1676</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>24</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.1813</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" t="n">
+        <v>34</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.5976</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.1274</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" t="n">
+        <v>38</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.5264</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.1789</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>6</v>
+      </c>
+      <c r="C50" t="n">
+        <v>52</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.2135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" t="n">
+        <v>46</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.1637</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" t="n">
+        <v>44</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.1747</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>9</v>
+      </c>
+      <c r="C53" t="n">
+        <v>76</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.2424</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>11</v>
+      </c>
+      <c r="C54" t="n">
+        <v>140</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4059</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>14</v>
+      </c>
+      <c r="C55" t="n">
+        <v>164</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.2836</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.3838</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" t="n">
+        <v>138</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3576</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>161</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.4893</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>17</v>
+      </c>
+      <c r="C58" t="n">
+        <v>190</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.2642</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3834</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" t="n">
+        <v>32</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.2139</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>19</v>
+      </c>
+      <c r="C60" t="n">
+        <v>83</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3017</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3474</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>20</v>
+      </c>
+      <c r="C61" t="n">
+        <v>23</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2817</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>21</v>
+      </c>
+      <c r="C62" t="n">
+        <v>32</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.2584</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>22</v>
+      </c>
+      <c r="C63" t="n">
+        <v>32</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.4039</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>23</v>
+      </c>
+      <c r="C64" t="n">
+        <v>28</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.2681</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>33</v>
+      </c>
+      <c r="C65" t="n">
+        <v>20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.4262</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.3184</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>34</v>
+      </c>
+      <c r="C66" t="n">
+        <v>29</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.3791</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>35</v>
+      </c>
+      <c r="C67" t="n">
+        <v>109</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.1536</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.5865</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>36</v>
+      </c>
+      <c r="C68" t="n">
+        <v>43</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>39</v>
+      </c>
+      <c r="C69" t="n">
+        <v>35</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.311</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>A  RavKav own alightings</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>40</v>
+      </c>
+      <c r="C70" t="n">
+        <v>40</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.3609</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="n">
+        <v>36</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.1921</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>46</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.5609</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.1968</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3</v>
+      </c>
+      <c r="C73" t="n">
+        <v>24</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.7519</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.06270000000000001</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>34</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1631</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>5</v>
+      </c>
+      <c r="C75" t="n">
+        <v>38</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.5167</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.1909</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6</v>
+      </c>
+      <c r="C76" t="n">
+        <v>52</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.2284</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>7</v>
+      </c>
+      <c r="C77" t="n">
+        <v>46</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.2242</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" t="n">
+        <v>44</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.1677</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>9</v>
+      </c>
+      <c r="C79" t="n">
+        <v>76</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.2811</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>11</v>
+      </c>
+      <c r="C80" t="n">
+        <v>140</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.3587</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>14</v>
+      </c>
+      <c r="C81" t="n">
+        <v>164</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.3277</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>15</v>
+      </c>
+      <c r="C82" t="n">
+        <v>138</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.2845</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>161</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.2292</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.4049</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>17</v>
+      </c>
+      <c r="C84" t="n">
+        <v>190</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.3507</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>18</v>
+      </c>
+      <c r="C85" t="n">
+        <v>32</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.2314</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>19</v>
+      </c>
+      <c r="C86" t="n">
+        <v>83</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.6203</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.1254</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>20</v>
+      </c>
+      <c r="C87" t="n">
+        <v>23</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.9337</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.0137</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>21</v>
+      </c>
+      <c r="C88" t="n">
+        <v>32</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.0436</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>22</v>
+      </c>
+      <c r="C89" t="n">
+        <v>32</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.4929</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.2309</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>23</v>
+      </c>
+      <c r="C90" t="n">
+        <v>28</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.5914</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.1667</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>33</v>
+      </c>
+      <c r="C91" t="n">
+        <v>20</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.5969</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.1803</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>34</v>
+      </c>
+      <c r="C92" t="n">
+        <v>29</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.5726</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.1629</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>35</v>
+      </c>
+      <c r="C93" t="n">
+        <v>109</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.8618</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.0265</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>36</v>
+      </c>
+      <c r="C94" t="n">
+        <v>43</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.0474</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>39</v>
+      </c>
+      <c r="C95" t="n">
+        <v>35</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>B  RavKav production x on-board</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>40</v>
+      </c>
+      <c r="C96" t="n">
+        <v>40</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.1344</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>36</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.6264999999999999</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.1698</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="n">
+        <v>46</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.5679</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.1878</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" t="n">
+        <v>24</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.1887</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>34</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.6012</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>5</v>
+      </c>
+      <c r="C101" t="n">
+        <v>38</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.2587</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C102" t="n">
+        <v>52</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.4337</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.2627</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>7</v>
+      </c>
+      <c r="C103" t="n">
+        <v>46</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.1933</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>8</v>
+      </c>
+      <c r="C104" t="n">
+        <v>44</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.1601</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>9</v>
+      </c>
+      <c r="C105" t="n">
+        <v>76</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.3845</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.265</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>11</v>
+      </c>
+      <c r="C106" t="n">
+        <v>140</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.3111</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>14</v>
+      </c>
+      <c r="C107" t="n">
+        <v>164</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.3541</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>15</v>
+      </c>
+      <c r="C108" t="n">
+        <v>138</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.2956</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>161</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.4433</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>17</v>
+      </c>
+      <c r="C110" t="n">
+        <v>190</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.3745</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>18</v>
+      </c>
+      <c r="C111" t="n">
+        <v>32</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.4786</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.2035</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>19</v>
+      </c>
+      <c r="C112" t="n">
+        <v>83</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.2808</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>20</v>
+      </c>
+      <c r="C113" t="n">
+        <v>23</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.3549</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>21</v>
+      </c>
+      <c r="C114" t="n">
+        <v>32</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.5958</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.1216</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>22</v>
+      </c>
+      <c r="C115" t="n">
+        <v>32</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.3061</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>23</v>
+      </c>
+      <c r="C116" t="n">
+        <v>28</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.4842</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.2113</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>33</v>
+      </c>
+      <c r="C117" t="n">
+        <v>20</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.3405</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>34</v>
+      </c>
+      <c r="C118" t="n">
+        <v>29</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.1998</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>35</v>
+      </c>
+      <c r="C119" t="n">
+        <v>109</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.2376</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>36</v>
+      </c>
+      <c r="C120" t="n">
+        <v>43</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5661</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.1622</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>39</v>
+      </c>
+      <c r="C121" t="n">
+        <v>35</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.1799</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>E  A to super-zone, B inside it</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>40</v>
+      </c>
+      <c r="C122" t="n">
+        <v>40</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.5458</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.1349</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="n">
+        <v>36</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.5411</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.1592</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2</v>
+      </c>
+      <c r="C124" t="n">
+        <v>46</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.2009</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>3</v>
+      </c>
+      <c r="C125" t="n">
+        <v>24</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3308</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" t="n">
+        <v>34</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.1539</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>5</v>
+      </c>
+      <c r="C127" t="n">
+        <v>38</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.2255</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>6</v>
+      </c>
+      <c r="C128" t="n">
+        <v>52</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.2387</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>7</v>
+      </c>
+      <c r="C129" t="n">
+        <v>46</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.227</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>8</v>
+      </c>
+      <c r="C130" t="n">
+        <v>44</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4603</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.2243</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>9</v>
+      </c>
+      <c r="C131" t="n">
+        <v>76</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.2785</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>11</v>
+      </c>
+      <c r="C132" t="n">
+        <v>140</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.348</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>14</v>
+      </c>
+      <c r="C133" t="n">
+        <v>164</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>15</v>
+      </c>
+      <c r="C134" t="n">
+        <v>138</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.3897</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>161</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.1796</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.4939</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>17</v>
+      </c>
+      <c r="C136" t="n">
+        <v>190</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.2136</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.4255</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>18</v>
+      </c>
+      <c r="C137" t="n">
+        <v>32</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.2168</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>19</v>
+      </c>
+      <c r="C138" t="n">
+        <v>83</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.3987</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>20</v>
+      </c>
+      <c r="C139" t="n">
+        <v>23</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3207</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>21</v>
+      </c>
+      <c r="C140" t="n">
+        <v>32</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.2388</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4116</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>22</v>
+      </c>
+      <c r="C141" t="n">
+        <v>32</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3518</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>23</v>
+      </c>
+      <c r="C142" t="n">
+        <v>28</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.3033</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>33</v>
+      </c>
+      <c r="C143" t="n">
+        <v>20</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.3471</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>34</v>
+      </c>
+      <c r="C144" t="n">
+        <v>29</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0.3779</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>35</v>
+      </c>
+      <c r="C145" t="n">
+        <v>109</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.1014</v>
+      </c>
+      <c r="E145" t="n">
+        <v>0.6745</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>36</v>
+      </c>
+      <c r="C146" t="n">
+        <v>43</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="E146" t="n">
+        <v>0.272</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>39</v>
+      </c>
+      <c r="C147" t="n">
+        <v>35</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.2189</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0.3901</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>C  current calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>40</v>
+      </c>
+      <c r="C148" t="n">
+        <v>40</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.2127</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0.4214</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="n">
+        <v>36</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="E149" t="n">
+        <v>0.3063</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2</v>
+      </c>
+      <c r="C150" t="n">
+        <v>46</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0.2079</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>3</v>
+      </c>
+      <c r="C151" t="n">
+        <v>24</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.1538</v>
+      </c>
+      <c r="E151" t="n">
+        <v>0.6347</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>4</v>
+      </c>
+      <c r="C152" t="n">
+        <v>34</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0.2522</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>5</v>
+      </c>
+      <c r="C153" t="n">
+        <v>38</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0.3302</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>6</v>
+      </c>
+      <c r="C154" t="n">
+        <v>52</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="E154" t="n">
+        <v>0.2759</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>7</v>
+      </c>
+      <c r="C155" t="n">
+        <v>46</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="E155" t="n">
+        <v>0.3225</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>8</v>
+      </c>
+      <c r="C156" t="n">
+        <v>44</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="E156" t="n">
+        <v>0.3338</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>9</v>
+      </c>
+      <c r="C157" t="n">
+        <v>76</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.2648</v>
+      </c>
+      <c r="E157" t="n">
+        <v>0.3922</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>11</v>
+      </c>
+      <c r="C158" t="n">
+        <v>140</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.4111</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>14</v>
+      </c>
+      <c r="C159" t="n">
+        <v>164</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="E159" t="n">
+        <v>0.3903</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>15</v>
+      </c>
+      <c r="C160" t="n">
+        <v>138</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0.3875</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>161</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.1593</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0.5011</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>17</v>
+      </c>
+      <c r="C162" t="n">
+        <v>190</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0.4678</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>18</v>
+      </c>
+      <c r="C163" t="n">
+        <v>32</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="E163" t="n">
+        <v>0.2481</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>19</v>
+      </c>
+      <c r="C164" t="n">
+        <v>83</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.1803</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.5579</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>20</v>
+      </c>
+      <c r="C165" t="n">
+        <v>23</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0.3622</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>21</v>
+      </c>
+      <c r="C166" t="n">
+        <v>32</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="E166" t="n">
+        <v>0.5699</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>22</v>
+      </c>
+      <c r="C167" t="n">
+        <v>32</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.2698</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0.421</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>23</v>
+      </c>
+      <c r="C168" t="n">
+        <v>28</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0.3788</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>33</v>
+      </c>
+      <c r="C169" t="n">
+        <v>20</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.1653</v>
+      </c>
+      <c r="E169" t="n">
+        <v>0.629</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>34</v>
+      </c>
+      <c r="C170" t="n">
+        <v>29</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="E170" t="n">
+        <v>0.5463</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>35</v>
+      </c>
+      <c r="C171" t="n">
+        <v>109</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.6496</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>36</v>
+      </c>
+      <c r="C172" t="n">
+        <v>43</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.2665</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0.3786</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>39</v>
+      </c>
+      <c r="C173" t="n">
+        <v>35</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.1296</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0.5716</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>D  on-board-prior calibrated layer (survey incl.)</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>40</v>
+      </c>
+      <c r="C174" t="n">
+        <v>40</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.1499</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.5715</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -39921,7 +44613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42940,7 +47632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42955,12 +47647,12 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="37" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
@@ -43283,25 +47975,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>volume the rule gives</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>gap from thin segments</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>diff % vs RavKav 2022</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>within ±15 % (RavKav 2022)</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>diff % vs RavKav 2025</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>within ±15 % (RavKav 2025)</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>class</t>
         </is>
@@ -43324,18 +48026,24 @@
         <v>0.51</v>
       </c>
       <c r="F15" t="n">
+        <v>2639.33</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-784.55</v>
+      </c>
+      <c r="H15" t="n">
         <v>4.3</v>
       </c>
-      <c r="G15" t="b">
+      <c r="I15" t="b">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>38.37</v>
       </c>
-      <c r="I15" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -43358,18 +48066,24 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="b">
+        <v>2802</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>34.49</v>
       </c>
-      <c r="I16" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43392,18 +48106,24 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>2158.43</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-663.0700000000001</v>
+      </c>
+      <c r="H17" t="n">
         <v>-23.5</v>
       </c>
-      <c r="G17" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>-29.36</v>
       </c>
-      <c r="I17" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43426,18 +48146,24 @@
         <v>0.76</v>
       </c>
       <c r="F18" t="n">
+        <v>1911.29</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>128.45</v>
       </c>
-      <c r="G18" t="b">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>124.49</v>
       </c>
-      <c r="I18" t="b">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -43460,18 +48186,24 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>3071</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>11.25</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43494,18 +48226,24 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>4122.51</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>-0</v>
       </c>
-      <c r="G20" t="b">
+      <c r="I20" t="b">
         <v>1</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>-15.57</v>
       </c>
-      <c r="I20" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43528,18 +48266,24 @@
         <v>0.77</v>
       </c>
       <c r="F21" t="n">
+        <v>3531.44</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>152.96</v>
       </c>
-      <c r="G21" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>150.31</v>
       </c>
-      <c r="I21" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -43562,18 +48306,24 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="b">
+        <v>2976.22</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="b">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>25.07</v>
       </c>
-      <c r="I22" t="b">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43596,18 +48346,24 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
+        <v>4409.43</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>-0</v>
-      </c>
-      <c r="G23" t="b">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5.38</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43630,18 +48386,24 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>144</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>-0</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-1.05</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43664,18 +48426,24 @@
         <v>0.15</v>
       </c>
       <c r="F25" t="n">
+        <v>1559.99</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>10.27</v>
-      </c>
-      <c r="G25" t="b">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-12.58</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="n">
+        <v>-12.58</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43698,18 +48466,24 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
+        <v>1434.44</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-770.28</v>
+      </c>
+      <c r="H26" t="n">
         <v>-34.94</v>
       </c>
-      <c r="G26" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>-67.81</v>
       </c>
-      <c r="I26" t="b">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43732,18 +48506,24 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
+        <v>2122.29</v>
+      </c>
+      <c r="G27" t="n">
+        <v>350.51</v>
+      </c>
+      <c r="H27" t="n">
         <v>19.79</v>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
         <v>-11.16</v>
       </c>
-      <c r="I27" t="b">
+      <c r="K27" t="b">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43766,18 +48546,24 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="b">
-        <v>1</v>
+        <v>4295.41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-8.65</v>
+        <v>0</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>-8.65</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43800,18 +48586,24 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="b">
-        <v>1</v>
+        <v>6214.47</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-10.22</v>
+        <v>0</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="n">
+        <v>-10.22</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43834,18 +48626,24 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
+        <v>5366.65</v>
+      </c>
+      <c r="G30" t="n">
+        <v>39.85</v>
+      </c>
+      <c r="H30" t="n">
         <v>0.75</v>
-      </c>
-      <c r="G30" t="b">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-11.1</v>
       </c>
       <c r="I30" t="b">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="n">
+        <v>-11.1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43868,18 +48666,24 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="b">
-        <v>1</v>
+        <v>6956.03</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -43902,18 +48706,24 @@
         <v>0.73</v>
       </c>
       <c r="F32" t="n">
+        <v>2602.25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>55.07</v>
       </c>
-      <c r="G32" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>90.53</v>
       </c>
-      <c r="I32" t="b">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -43936,18 +48746,24 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
+        <v>11584.14</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
         <v>369.46</v>
       </c>
-      <c r="G33" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>261.76</v>
       </c>
-      <c r="I33" t="b">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -43970,18 +48786,24 @@
         <v>0.46</v>
       </c>
       <c r="F34" t="n">
+        <v>3250.98</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-186.02</v>
+      </c>
+      <c r="H34" t="n">
         <v>17.96</v>
       </c>
-      <c r="G34" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>8.039999999999999</v>
       </c>
-      <c r="I34" t="b">
+      <c r="K34" t="b">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44004,18 +48826,24 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="F35" t="n">
+        <v>2834.34</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-737.6900000000001</v>
+      </c>
+      <c r="H35" t="n">
         <v>76.48</v>
       </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>68.75</v>
       </c>
-      <c r="I35" t="b">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44038,18 +48866,24 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
+        <v>2778.38</v>
+      </c>
+      <c r="G36" t="n">
+        <v>147.1</v>
+      </c>
+      <c r="H36" t="n">
         <v>5.59</v>
       </c>
-      <c r="G36" t="b">
+      <c r="I36" t="b">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>16.02</v>
       </c>
-      <c r="I36" t="b">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44072,18 +48906,24 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
+        <v>1808.1</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-66.84999999999999</v>
+      </c>
+      <c r="H37" t="n">
         <v>136.29</v>
       </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>178.09</v>
       </c>
-      <c r="I37" t="b">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44106,18 +48946,24 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
+        <v>2151.01</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-278.2</v>
+      </c>
+      <c r="H38" t="n">
         <v>-11.45</v>
-      </c>
-      <c r="G38" t="b">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
-        <v>2.12</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K38" t="b">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44140,18 +48986,24 @@
         <v>0.78</v>
       </c>
       <c r="F39" t="n">
+        <v>1020.98</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-162.16</v>
+      </c>
+      <c r="H39" t="n">
         <v>76.7</v>
       </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>52.32</v>
       </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="K39" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44174,18 +49026,24 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
+        <v>1016.5</v>
+      </c>
+      <c r="G40" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="H40" t="n">
         <v>277.61</v>
       </c>
-      <c r="G40" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
         <v>154.31</v>
       </c>
-      <c r="I40" t="b">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44208,18 +49066,24 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
+        <v>764.49</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="H41" t="n">
         <v>-0</v>
-      </c>
-      <c r="G41" t="b">
-        <v>1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-6.6</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44242,18 +49106,24 @@
         <v>0.87</v>
       </c>
       <c r="F42" t="n">
+        <v>1590.98</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-204.65</v>
+      </c>
+      <c r="H42" t="n">
         <v>73.66</v>
       </c>
-      <c r="G42" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>73.27</v>
       </c>
-      <c r="I42" t="b">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44276,18 +49146,24 @@
         <v>1</v>
       </c>
       <c r="F43" t="n">
+        <v>2980.74</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-13.25</v>
+      </c>
+      <c r="H43" t="n">
         <v>303.5</v>
       </c>
-      <c r="G43" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
         <v>182.85</v>
       </c>
-      <c r="I43" t="b">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44310,18 +49186,24 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
+        <v>2767.53</v>
+      </c>
+      <c r="G44" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="H44" t="n">
         <v>209.28</v>
       </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
         <v>159.92</v>
       </c>
-      <c r="I44" t="b">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44344,18 +49226,24 @@
         <v>0.1</v>
       </c>
       <c r="F45" t="n">
+        <v>4971.02</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-195.71</v>
+      </c>
+      <c r="H45" t="n">
         <v>6.42</v>
-      </c>
-      <c r="G45" t="b">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
-        <v>4.02</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="K45" t="b">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44378,18 +49266,24 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
+        <v>4256.71</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-188.6</v>
+      </c>
+      <c r="H46" t="n">
         <v>-4.24</v>
-      </c>
-      <c r="G46" t="b">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-10.94</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J46" t="n">
+        <v>-10.94</v>
+      </c>
+      <c r="K46" t="b">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44412,18 +49306,24 @@
         <v>1</v>
       </c>
       <c r="F47" t="n">
+        <v>1916.87</v>
+      </c>
+      <c r="G47" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="H47" t="n">
         <v>179.87</v>
       </c>
-      <c r="G47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
         <v>212.8</v>
       </c>
-      <c r="I47" t="b">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44446,18 +49346,24 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
+        <v>2019.01</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0</v>
       </c>
-      <c r="G48" t="b">
+      <c r="I48" t="b">
         <v>1</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>-27.98</v>
       </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -44480,18 +49386,24 @@
         <v>0.67</v>
       </c>
       <c r="F49" t="n">
+        <v>4562.95</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-372.75</v>
+      </c>
+      <c r="H49" t="n">
         <v>61.14</v>
       </c>
-      <c r="G49" t="b">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>60</v>
       </c>
-      <c r="I49" t="b">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>mostly guarded (survey volume kept)</t>
         </is>
@@ -44514,18 +49426,24 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
+        <v>4839.04</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-71.38</v>
+      </c>
+      <c r="H50" t="n">
         <v>-1.45</v>
       </c>
-      <c r="G50" t="b">
+      <c r="I50" t="b">
         <v>1</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>-21.6</v>
       </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>mostly anchored (RavKav volume)</t>
         </is>
@@ -45114,1340 +50032,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>T15_rail_stations</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>obs_total</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>mod_total</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>total_diff_pct</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>slope_origin</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>R2_origin</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>MAE</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>RMSE</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>RMSE_pct</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>station-pair matrix, common stations</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>182</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1799.472</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-50.721</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9360000000000001</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.945</v>
-      </c>
-      <c r="I4" t="n">
-        <v>10.669</v>
-      </c>
-      <c r="J4" t="n">
-        <v>28.638</v>
-      </c>
-      <c r="K4" t="n">
-        <v>142.735</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.749</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>station entries</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>14</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1799.472</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-50.721</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I5" t="n">
-        <v>132.294</v>
-      </c>
-      <c r="J5" t="n">
-        <v>186.082</v>
-      </c>
-      <c r="K5" t="n">
-        <v>71.343</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.861</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>station entries, after one scale factor (2.03)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.944</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.982</v>
-      </c>
-      <c r="I6" t="n">
-        <v>38.867</v>
-      </c>
-      <c r="J6" t="n">
-        <v>48.033</v>
-      </c>
-      <c r="K6" t="n">
-        <v>18.416</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.861</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>station exits</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1799.472</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-50.721</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="I7" t="n">
-        <v>132.294</v>
-      </c>
-      <c r="J7" t="n">
-        <v>228.123</v>
-      </c>
-      <c r="K7" t="n">
-        <v>87.461</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.847</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>station exits, after one scale factor (2.03)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>14</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3651.593</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.964</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.976</v>
-      </c>
-      <c r="I8" t="n">
-        <v>43.344</v>
-      </c>
-      <c r="J8" t="n">
-        <v>68.444</v>
-      </c>
-      <c r="K8" t="n">
-        <v>26.241</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.847</v>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>T15_rail_station_size_classes</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>what</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>version</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>class</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>obs_mean</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>RMSE_pct</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>limit_pct</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" t="n">
-        <v>56.712</v>
-      </c>
-      <c r="F14" t="n">
-        <v>41.326</v>
-      </c>
-      <c r="G14" t="n">
-        <v>50</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>100-250</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" t="n">
-        <v>173.236</v>
-      </c>
-      <c r="F15" t="n">
-        <v>50.135</v>
-      </c>
-      <c r="G15" t="n">
-        <v>40</v>
-      </c>
-      <c r="H15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>250-500</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="n">
-        <v>493.552</v>
-      </c>
-      <c r="F16" t="n">
-        <v>56.423</v>
-      </c>
-      <c r="G16" t="n">
-        <v>30</v>
-      </c>
-      <c r="H16" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>500-750</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>612.062</v>
-      </c>
-      <c r="F17" t="n">
-        <v>52.168</v>
-      </c>
-      <c r="G17" t="n">
-        <v>20</v>
-      </c>
-      <c r="H17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>750-1000</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
-        <v>873.427</v>
-      </c>
-      <c r="F18" t="n">
-        <v>55.653</v>
-      </c>
-      <c r="G18" t="n">
-        <v>15</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>56.712</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.513</v>
-      </c>
-      <c r="G19" t="n">
-        <v>50</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>100-250</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>173.236</v>
-      </c>
-      <c r="F20" t="n">
-        <v>27.735</v>
-      </c>
-      <c r="G20" t="n">
-        <v>40</v>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>250-500</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>493.552</v>
-      </c>
-      <c r="F21" t="n">
-        <v>11.572</v>
-      </c>
-      <c r="G21" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>500-750</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>612.062</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.936</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>entries</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>750-1000</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>873.427</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10.008</v>
-      </c>
-      <c r="G23" t="n">
-        <v>15</v>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="n">
-        <v>41.351</v>
-      </c>
-      <c r="F24" t="n">
-        <v>53.145</v>
-      </c>
-      <c r="G24" t="n">
-        <v>50</v>
-      </c>
-      <c r="H24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>100-250</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>133.792</v>
-      </c>
-      <c r="F25" t="n">
-        <v>59.478</v>
-      </c>
-      <c r="G25" t="n">
-        <v>40</v>
-      </c>
-      <c r="H25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>500-750</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>676.163</v>
-      </c>
-      <c r="F26" t="n">
-        <v>35.212</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20</v>
-      </c>
-      <c r="H26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>750-1000</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>870.867</v>
-      </c>
-      <c r="F27" t="n">
-        <v>55.732</v>
-      </c>
-      <c r="G27" t="n">
-        <v>15</v>
-      </c>
-      <c r="H27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>as is</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>1000+</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1187.5</v>
-      </c>
-      <c r="F28" t="n">
-        <v>53.376</v>
-      </c>
-      <c r="G28" t="n">
-        <v>12</v>
-      </c>
-      <c r="H28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0-100</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>6</v>
-      </c>
-      <c r="E29" t="n">
-        <v>41.351</v>
-      </c>
-      <c r="F29" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="G29" t="n">
-        <v>50</v>
-      </c>
-      <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>100-250</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>5</v>
-      </c>
-      <c r="E30" t="n">
-        <v>133.792</v>
-      </c>
-      <c r="F30" t="n">
-        <v>24.469</v>
-      </c>
-      <c r="G30" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>500-750</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>676.163</v>
-      </c>
-      <c r="F31" t="n">
-        <v>31.472</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>750-1000</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>870.867</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10.169</v>
-      </c>
-      <c r="G32" t="n">
-        <v>15</v>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>exits</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>scaled</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1000+</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>1187.5</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5.388</v>
-      </c>
-      <c r="G33" t="n">
-        <v>12</v>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>T15_rail_origins_by_superzone</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Unnamed: 0</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>survey rail 2022 (door-to-door)</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>station 2019 x 0.793</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>rail 2025 stations</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" t="n">
-        <v>566.8</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1951.4</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2</v>
-      </c>
-      <c r="B40" t="n">
-        <v>818.8</v>
-      </c>
-      <c r="C40" t="n">
-        <v>576.1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1168.6</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B41" t="n">
-        <v>440.6</v>
-      </c>
-      <c r="C41" t="n">
-        <v>526.9</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1279.9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B42" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>6</v>
-      </c>
-      <c r="B43" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="C43" t="n">
-        <v>557.6</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>8</v>
-      </c>
-      <c r="B44" t="n">
-        <v>255.6</v>
-      </c>
-      <c r="C44" t="n">
-        <v>167</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1303.4</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>11</v>
-      </c>
-      <c r="B45" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>12</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" t="n">
-        <v>304.4</v>
-      </c>
-      <c r="D46" t="n">
-        <v>500.8</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>13</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
-        <v>160.1</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>14</v>
-      </c>
-      <c r="B48" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>15</v>
-      </c>
-      <c r="B49" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="C49" t="n">
-        <v>234</v>
-      </c>
-      <c r="D49" t="n">
-        <v>599.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>16</v>
-      </c>
-      <c r="B50" t="n">
-        <v>91.90000000000001</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>17</v>
-      </c>
-      <c r="B51" t="n">
-        <v>35</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>21</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" t="n">
-        <v>116.1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>207.6</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>22</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" t="n">
-        <v>155.9</v>
-      </c>
-      <c r="D53" t="n">
-        <v>346.9</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>24</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>181.7</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>25</v>
-      </c>
-      <c r="B55" t="n">
-        <v>138.7</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>34</v>
-      </c>
-      <c r="B56" t="n">
-        <v>301.8</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>36</v>
-      </c>
-      <c r="B57" t="n">
-        <v>277.5</v>
-      </c>
-      <c r="C57" t="n">
-        <v>304.5</v>
-      </c>
-      <c r="D57" t="n">
-        <v>709.5</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>37</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>114.1</v>
-      </c>
-      <c r="D58" t="n">
-        <v>314.3</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>39</v>
-      </c>
-      <c r="B59" t="n">
-        <v>554.9</v>
-      </c>
-      <c r="C59" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D59" t="n">
-        <v>508.1</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>40</v>
-      </c>
-      <c r="B60" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="C60" t="n">
-        <v>141.6</v>
-      </c>
-      <c r="D60" t="n">
-        <v>205.4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>